--- a/outputs/evaluation/decision/v1/CF_M05/run_1/CF_M05_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M05/run_1/CF_M05_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,51 +471,551 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>AD_01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Aquest microservei té com a funció principal l’encaminament de totes les comunicacions cap al microservei corresponent dins de l’arquitectura del sistema.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AU_08, C_05</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AU_08</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AU_08; 12a. Speed and latency</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Leader Service</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>CF_M05_AD04</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6762</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AD_03</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A més de la seva funció com a portal, aquest microservei incorpora els binaris necessaris per al frontEnd tant del mateix portal com de la resta d’aplicacions del portal.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AU_09, C_01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AU_09; 10a. Appearance</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Portal Service</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CF_M05_AD03</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7266</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>El microservei Access Control té com a objectiu principal la gestió d’autenticació d’usuaris i els seus permisos dins de l’aplicació.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AU_10, R_48</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AU_10; El sistema ha de disposar d’un mecanisme segur d’autenticació i verificació de permisos per assegurar que cada usuari només pugui accedir a la informació i funcionalitats que li corresponen.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Access Control Service</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CF_M05_AD04</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6817</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>El microservei Communication Log té com a finalitat principal registrar totes les comunicacions que es produeixen dins del sistema, tant entre microserveis com amb serveis externs.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AU_11, C_09</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AU_11; 15b. Integrity</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Communication Log Service</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CF_M05_AD05</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>This component acts as a traceability and audit mechanism, ensuring that each interaction is documented for later analysis, incident resolution and regulatory compliance.</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7118</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Té com a funció principal la planificació i programació de processos dins del sistema.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AU_12, C_06</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AU_12; 12a. Availability</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scheduler Service</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>CF_M05_AD08</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0.6084000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>En el present projecte, el client s’ha desenvolupat amb Angular, implementant una Single-PageApplication (SPA) que renderitza vistes dinàmiques i gestiona la navegació interna sense haver de recarregar la pàgina, millorant la fluïdesa d’ús.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AU_13, P_03, C_02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AU_13, P_03</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>61, 62</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AU_13; P_03; 11a. Usability</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Angular; MVVM</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>CF_M05_AD09</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> It allows you to create dynamic, interactive and scalable user interfaces, facilitating the development and maintenance of large applications.</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.7027</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>AD_08</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>C_02</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Pel servidor s’ha utilitzat Spring Boot, que proporciona una plataforma per exposar una API REST.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AU_14, P_04, C_05</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AU_14, P_04</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>11a. Usability</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MVVM</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>CF_M05_AD10</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0.6768999999999999</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>AU_14; P_04; 12a. Speed and latency</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Spring Boot; Layered Architecture</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>CF_M05_AD11</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>It allows you to automate the deployment, scaling and management of applications running in containers, run thousands of containers on different servers and ensure high availability.</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.6495</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AD_09</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>El protocol d’intercanvi de missatges que es fa servir en aquest cas és HTTP i el format de dades emprat és JSON.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AU_15, C_05</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>AU_15; 12a. Speed and latency</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.6165</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AD_10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>El proveïdor per aquest projecte és Amazon Web Services el qual té un ampli catàleg de serveis i recursos cloud.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AU_17, C_06</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AU_17</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AU_17; 12a. Availability</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6708</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AD_11</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pel desplegament de l’aplicació s’ha fet ús d’Amazon EKS, un servei que ofereix AWS el qual permet utilitzar Kubernetes (K8s), una plataforma d’orquestració de contenidors creada per Google, sense necessitat d’instal·lar-la ni mantenir-la.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AU_18, AU_19, C_06</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AU_18, AU_19</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AU_18; AU_19; 12a. Availability</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Amazon EKS; Kubernetes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CF_M05_AD06</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>The use of this type of architecture allows high scalability, availability and accessibility, since resource management can be done according to needs and anywhere with an Internet connection. It also reduces maintainability, managed by resource providers, and without major expenses, since you pay for the resources consumed.</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6858</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AD_12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>L’aplicació segueix el patró Client-Servidor el qual organitza el codi en dos components diferenciats: el client, que formula sol·licituds de servei, i el servidor, que les rep, les processa i retorna respostes.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P_01, C_05</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>P_01; 12a. Speed and latency</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Client-Server</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CF_M05_AD08</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>This separation of responsibilities allows [...] the server to focus on business logic, security, data integrity, and persistence.</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6850000000000001</v>
       </c>
     </row>
   </sheetData>
